--- a/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
+++ b/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
@@ -3709,7 +3709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="H5" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G5,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G5))</f>
+        <f>IF(I5=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G5,$A$5:$A$1000,I5))</f>
         <v/>
       </c>
       <c r="I5" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G5)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G5)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -3846,11 +3846,11 @@
         </is>
       </c>
       <c r="H6" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G6,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G6))</f>
+        <f>IF(I6=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G6,$A$5:$A$1000,I6))</f>
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G6)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G6)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -3882,11 +3882,11 @@
         </is>
       </c>
       <c r="H7" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G7,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G7))</f>
+        <f>IF(I7=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G7,$A$5:$A$1000,I7))</f>
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G7)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G7)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -3918,11 +3918,11 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G8,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G8))</f>
+        <f>IF(I8=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G8,$A$5:$A$1000,I8))</f>
         <v/>
       </c>
       <c r="I8" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G8)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G8)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -3954,11 +3954,11 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G9,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G9))</f>
+        <f>IF(I9=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G9,$A$5:$A$1000,I9))</f>
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G9)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G9)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -3990,11 +3990,11 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G10,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G10))</f>
+        <f>IF(I10=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G10,$A$5:$A$1000,I10))</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G10)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G10)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4026,11 +4026,11 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G11,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G11))</f>
+        <f>IF(I11=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G11,$A$5:$A$1000,I11))</f>
         <v/>
       </c>
       <c r="I11" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G11)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G11)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4062,11 +4062,11 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G12,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G12))</f>
+        <f>IF(I12=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G12,$A$5:$A$1000,I12))</f>
         <v/>
       </c>
       <c r="I12" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G12)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G12)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4098,11 +4098,11 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G13,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G13))</f>
+        <f>IF(I13=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G13,$A$5:$A$1000,I13))</f>
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G13)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G13)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4134,11 +4134,11 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G14,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G14))</f>
+        <f>IF(I14=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G14,$A$5:$A$1000,I14))</f>
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G14)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G14)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4170,11 +4170,11 @@
         </is>
       </c>
       <c r="H15" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G15,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G15))</f>
+        <f>IF(I15=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G15,$A$5:$A$1000,I15))</f>
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G15)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G15)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4202,11 +4202,11 @@
         </is>
       </c>
       <c r="H16" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G16,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G16))</f>
+        <f>IF(I16=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G16,$A$5:$A$1000,I16))</f>
         <v/>
       </c>
       <c r="I16" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G16)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G16)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4234,11 +4234,11 @@
         </is>
       </c>
       <c r="H17" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G17,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G17))</f>
+        <f>IF(I17=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G17,$A$5:$A$1000,I17))</f>
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G17)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G17)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4266,11 +4266,11 @@
         </is>
       </c>
       <c r="H18" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G18,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G18))</f>
+        <f>IF(I18=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G18,$A$5:$A$1000,I18))</f>
         <v/>
       </c>
       <c r="I18" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G18)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G18)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4302,11 +4302,11 @@
         </is>
       </c>
       <c r="H19" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G19,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G19))</f>
+        <f>IF(I19=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G19,$A$5:$A$1000,I19))</f>
         <v/>
       </c>
       <c r="I19" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G19)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G19)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4338,11 +4338,11 @@
         </is>
       </c>
       <c r="H20" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G20,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G20))</f>
+        <f>IF(I20=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G20,$A$5:$A$1000,I20))</f>
         <v/>
       </c>
       <c r="I20" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G20)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G20)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4374,11 +4374,11 @@
         </is>
       </c>
       <c r="H21" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G21,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G21))</f>
+        <f>IF(I21=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G21,$A$5:$A$1000,I21))</f>
         <v/>
       </c>
       <c r="I21" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G21)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G21)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="H22" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G22,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G22))</f>
+        <f>IF(I22=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G22,$A$5:$A$1000,I22))</f>
         <v/>
       </c>
       <c r="I22" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G22)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G22)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4446,11 +4446,11 @@
         </is>
       </c>
       <c r="H23" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G23,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G23))</f>
+        <f>IF(I23=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G23,$A$5:$A$1000,I23))</f>
         <v/>
       </c>
       <c r="I23" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G23)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G23)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4478,11 +4478,11 @@
         </is>
       </c>
       <c r="H24" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G24,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G24))</f>
+        <f>IF(I24=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G24,$A$5:$A$1000,I24))</f>
         <v/>
       </c>
       <c r="I24" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G24)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G24)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="H25" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G25,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G25))</f>
+        <f>IF(I25=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G25,$A$5:$A$1000,I25))</f>
         <v/>
       </c>
       <c r="I25" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G25)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G25)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4546,11 +4546,11 @@
         </is>
       </c>
       <c r="H26" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G26,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G26))</f>
+        <f>IF(I26=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G26,$A$5:$A$1000,I26))</f>
         <v/>
       </c>
       <c r="I26" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G26)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G26)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4582,11 +4582,11 @@
         </is>
       </c>
       <c r="H27" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G27,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G27))</f>
+        <f>IF(I27=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G27,$A$5:$A$1000,I27))</f>
         <v/>
       </c>
       <c r="I27" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G27)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G27)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4618,11 +4618,11 @@
         </is>
       </c>
       <c r="H28" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G28,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G28))</f>
+        <f>IF(I28=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G28,$A$5:$A$1000,I28))</f>
         <v/>
       </c>
       <c r="I28" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G28)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G28)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4650,11 +4650,11 @@
         </is>
       </c>
       <c r="H29" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G29,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G29))</f>
+        <f>IF(I29=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G29,$A$5:$A$1000,I29))</f>
         <v/>
       </c>
       <c r="I29" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G29)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G29)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="H30" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G30,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G30))</f>
+        <f>IF(I30=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G30,$A$5:$A$1000,I30))</f>
         <v/>
       </c>
       <c r="I30" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G30)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G30)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4722,11 +4722,11 @@
         </is>
       </c>
       <c r="H31" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G31,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G31))</f>
+        <f>IF(I31=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G31,$A$5:$A$1000,I31))</f>
         <v/>
       </c>
       <c r="I31" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G31)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G31)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4758,11 +4758,11 @@
         </is>
       </c>
       <c r="H32" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G32,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G32))</f>
+        <f>IF(I32=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G32,$A$5:$A$1000,I32))</f>
         <v/>
       </c>
       <c r="I32" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G32)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G32)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="H33" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G33,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G33))</f>
+        <f>IF(I33=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G33,$A$5:$A$1000,I33))</f>
         <v/>
       </c>
       <c r="I33" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G33)</f>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G33)*$A$5:$A$1000))</f>
         <v/>
       </c>
     </row>
@@ -4830,14 +4830,15 @@
         </is>
       </c>
       <c r="H34" s="7">
-        <f>SUMIFS($D$5:$D$1000,$C$5:$C$1000,G34,$A$5:$A$1000,_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G34))</f>
+        <f>IF(I34=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G34,$A$5:$A$1000,I34))</f>
         <v/>
       </c>
       <c r="I34" s="11">
-        <f>_xlfn.MAXIFS($A$5:$A$1000,$C$5:$C$1000,G34)</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G34)*$A$5:$A$1000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
@@ -4845,6 +4846,169 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>

--- a/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
+++ b/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1363,17 +1363,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Claim and complete Clutch, G2 and DesignRush profiles; ask five clients for reviews.</t>
+          <t>Complete and optimise the Google Business Profile: services, price range, AEST hours, photos, and a review request to five recent clients.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>External: clutch.co, g2.com, designrush.com</t>
+          <t>External: business.google.com (Surry Hills listing)</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Profiles complete with pricing, turnaround, AEST hours; five reviews within 60 days.</t>
+          <t>Category "Graphic designer", services list matching the six target questions, price range from $545/mo, 10+ recent photos, five new reviews in 60 days.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1389,17 +1389,17 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.aipeekaboo.com/</t>
+          <t>https://business.google.com/</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>Profiles live; reviews visible; G2 citations rise in the Peekaboo sources table.</t>
+          <t>Live check: ask ChatGPT "graphic design services Sydney" monthly and confirm Design Bees still appears; profile shows the price range and services.</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Peekaboo cites g2.com 3 times with no claimed profile. HubSpot share of voice 0/10 on ChatGPT and Gemini.</t>
+          <t>11 Sep live check: ChatGPT returned the Google map pack for the Sydney query and Design Bees ranked first, so the profile is doing the work Peekaboo scores as 0. Peekaboo under-reports this.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2345,132 @@
       <c r="M32" s="4" t="inlineStr">
         <is>
           <t>Export still shows encoded URLs such as the XV Premium and Pappa Flock case studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>T29</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Off-site authority</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Claim and complete Clutch, G2 and DesignRush profiles; ask five clients for reviews.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>External: clutch.co, g2.com, designrush.com</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Profiles complete with pricing, turnaround, AEST hours; five reviews within 60 days.</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aipeekaboo.com/</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Profiles live; reviews visible; G2 citations rise in the Peekaboo sources table.</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Peekaboo cites g2.com 3 times with no claimed profile. HubSpot share of voice 0/10 on ChatGPT and Gemini. Was T13 before the 11 Sep live checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Content refresh</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Strengthen the post the engines already cite: /post/are-unlimited-graphic-design-services-truly-limitless-what-you-need-to-know.</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Wix Blog &gt; that post</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Add the $545 entry price, an AEST turnaround line, and an FAQ block with FAQPage schema; link to the pricing guide and the Design Pickle comparison.</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>AJ / Claude</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.designbees.com.au/post/are-unlimited-graphic-design-services-truly-limitless-what-you-need-to-know</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Re-run the six prompts monthly; this URL keeps appearing as the cited source and now quotes the price correctly.</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep live check: cited by ChatGPT and by Google AI Mode across several of the six queries. It is the strongest citation asset the site has.</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3814,11 +3940,11 @@
         </is>
       </c>
       <c r="H5" s="7">
-        <f>IF(I5=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G5,$A$5:$A$1000,I5))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G5)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G5)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I5" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G5)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G5)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G5)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -3846,11 +3972,11 @@
         </is>
       </c>
       <c r="H6" s="7">
-        <f>IF(I6=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G6,$A$5:$A$1000,I6))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G6)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G6)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G6)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G6)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G6)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -3882,11 +4008,11 @@
         </is>
       </c>
       <c r="H7" s="7">
-        <f>IF(I7=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G7,$A$5:$A$1000,I7))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G7)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G7)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G7)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G7)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G7)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -3918,11 +4044,11 @@
         </is>
       </c>
       <c r="H8" s="7">
-        <f>IF(I8=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G8,$A$5:$A$1000,I8))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G8)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G8)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I8" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G8)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G8)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G8)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -3954,11 +4080,11 @@
         </is>
       </c>
       <c r="H9" s="7">
-        <f>IF(I9=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G9,$A$5:$A$1000,I9))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G9)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G9)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G9)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G9)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G9)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -3990,11 +4116,11 @@
         </is>
       </c>
       <c r="H10" s="7">
-        <f>IF(I10=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G10,$A$5:$A$1000,I10))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G10)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G10)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G10)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G10)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G10)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4026,11 +4152,11 @@
         </is>
       </c>
       <c r="H11" s="7">
-        <f>IF(I11=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G11,$A$5:$A$1000,I11))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G11)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G11)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I11" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G11)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G11)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G11)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4062,11 +4188,11 @@
         </is>
       </c>
       <c r="H12" s="7">
-        <f>IF(I12=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G12,$A$5:$A$1000,I12))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G12)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G12)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I12" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G12)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G12)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G12)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4098,11 +4224,11 @@
         </is>
       </c>
       <c r="H13" s="7">
-        <f>IF(I13=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G13,$A$5:$A$1000,I13))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G13)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G13)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G13)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G13)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G13)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4134,11 +4260,11 @@
         </is>
       </c>
       <c r="H14" s="7">
-        <f>IF(I14=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G14,$A$5:$A$1000,I14))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G14)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G14)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G14)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G14)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G14)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4170,11 +4296,11 @@
         </is>
       </c>
       <c r="H15" s="7">
-        <f>IF(I15=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G15,$A$5:$A$1000,I15))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G15)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G15)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G15)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G15)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G15)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4202,11 +4328,11 @@
         </is>
       </c>
       <c r="H16" s="7">
-        <f>IF(I16=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G16,$A$5:$A$1000,I16))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G16)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G16)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I16" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G16)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G16)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G16)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4234,11 +4360,11 @@
         </is>
       </c>
       <c r="H17" s="7">
-        <f>IF(I17=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G17,$A$5:$A$1000,I17))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G17)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G17)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G17)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G17)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G17)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4266,11 +4392,11 @@
         </is>
       </c>
       <c r="H18" s="7">
-        <f>IF(I18=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G18,$A$5:$A$1000,I18))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G18)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G18)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I18" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G18)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G18)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G18)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4302,11 +4428,11 @@
         </is>
       </c>
       <c r="H19" s="7">
-        <f>IF(I19=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G19,$A$5:$A$1000,I19))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G19)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G19)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I19" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G19)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G19)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G19)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4338,11 +4464,11 @@
         </is>
       </c>
       <c r="H20" s="7">
-        <f>IF(I20=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G20,$A$5:$A$1000,I20))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G20)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G20)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I20" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G20)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G20)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G20)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4374,11 +4500,11 @@
         </is>
       </c>
       <c r="H21" s="7">
-        <f>IF(I21=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G21,$A$5:$A$1000,I21))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G21)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G21)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I21" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G21)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G21)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G21)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4410,11 +4536,11 @@
         </is>
       </c>
       <c r="H22" s="7">
-        <f>IF(I22=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G22,$A$5:$A$1000,I22))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G22)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G22)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I22" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G22)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G22)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G22)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4446,11 +4572,11 @@
         </is>
       </c>
       <c r="H23" s="7">
-        <f>IF(I23=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G23,$A$5:$A$1000,I23))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G23)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G23)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I23" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G23)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G23)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G23)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4478,11 +4604,11 @@
         </is>
       </c>
       <c r="H24" s="7">
-        <f>IF(I24=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G24,$A$5:$A$1000,I24))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G24)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G24)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I24" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G24)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G24)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G24)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4514,11 +4640,11 @@
         </is>
       </c>
       <c r="H25" s="7">
-        <f>IF(I25=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G25,$A$5:$A$1000,I25))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G25)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G25)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I25" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G25)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G25)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G25)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4546,11 +4672,11 @@
         </is>
       </c>
       <c r="H26" s="7">
-        <f>IF(I26=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G26,$A$5:$A$1000,I26))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G26)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G26)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I26" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G26)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G26)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G26)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4582,11 +4708,11 @@
         </is>
       </c>
       <c r="H27" s="7">
-        <f>IF(I27=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G27,$A$5:$A$1000,I27))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G27)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G27)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I27" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G27)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G27)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G27)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4618,11 +4744,11 @@
         </is>
       </c>
       <c r="H28" s="7">
-        <f>IF(I28=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G28,$A$5:$A$1000,I28))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G28)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G28)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I28" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G28)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G28)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G28)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4650,11 +4776,11 @@
         </is>
       </c>
       <c r="H29" s="7">
-        <f>IF(I29=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G29,$A$5:$A$1000,I29))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G29)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G29)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I29" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G29)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G29)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G29)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4686,11 +4812,11 @@
         </is>
       </c>
       <c r="H30" s="7">
-        <f>IF(I30=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G30,$A$5:$A$1000,I30))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G30)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G30)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I30" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G30)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G30)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G30)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4722,11 +4848,11 @@
         </is>
       </c>
       <c r="H31" s="7">
-        <f>IF(I31=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G31,$A$5:$A$1000,I31))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G31)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G31)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I31" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G31)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G31)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G31)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4758,11 +4884,11 @@
         </is>
       </c>
       <c r="H32" s="7">
-        <f>IF(I32=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G32,$A$5:$A$1000,I32))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G32)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G32)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I32" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G32)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G32)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G32)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4794,11 +4920,11 @@
         </is>
       </c>
       <c r="H33" s="7">
-        <f>IF(I33=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G33,$A$5:$A$1000,I33))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G33)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G33)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I33" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G33)*$A$5:$A$1000))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G33)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G33)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
     </row>
@@ -4830,190 +4956,121 @@
         </is>
       </c>
       <c r="H34" s="7">
-        <f>IF(I34=0,"",SUMIFS($D$5:$D$1000,$C$5:$C$1000,G34,$A$5:$A$1000,I34))</f>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G34)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G34)*(ROW($C$5:$C$1000)-4)))))</f>
         <v/>
       </c>
       <c r="I34" s="11">
-        <f>SUMPRODUCT(MAX(($C$5:$C$1000=G34)*$A$5:$A$1000))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35"/>
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G34)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G34)*(ROW($C$5:$C$1000)-4)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Manual AI check</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT names Design Bees for "best unlimited graphic design subscription in Australia" (1 = yes)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep live check from AJ's own browser: named</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>ChatGPT: target queries naming Design Bees (of 6)</t>
+        </is>
+      </c>
+      <c r="H35" s="7">
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G35)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G35)*(ROW($C$5:$C$1000)-4)))))</f>
+        <v/>
+      </c>
+      <c r="I35" s="11">
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G35)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G35)*(ROW($C$5:$C$1000)-4)))))</f>
+        <v/>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Legend: fill columns A–E only; one row per metric per reading; keep the Metric text identical each time so the Latest block matches it. Numbers only in Value (use 1/0 for yes/no).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
+      <c r="A36" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Manual AI check</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT: target queries naming Design Bees (of 6)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep live check; only the freelancer question missed</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Google AI Mode: target queries naming Design Bees (of 6)</t>
+        </is>
+      </c>
+      <c r="H36" s="7">
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G36)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($D$5:$D$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G36)*(ROW($C$5:$C$1000)-4)))))</f>
+        <v/>
+      </c>
+      <c r="I36" s="11">
+        <f>IF(SUMPRODUCT(MAX(($C$5:$C$1000=$G36)*(ROW($C$5:$C$1000)-4)))=0,"",INDEX($A$5:$A$1000,SUMPRODUCT(MAX(($C$5:$C$1000=$G36)*(ROW($C$5:$C$1000)-4)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Manual AI check</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Google AI Mode: target queries naming Design Bees (of 6)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep live check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Legend: fill columns A–E only; one row per metric per reading; keep the Metric text identical each time so the Latest block matches it. Numbers only in Value (use 1/0 for yes/no). Add new readings at the bottom — the Latest block reads the last row for each metric. Leave column A to dates only.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
+++ b/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
@@ -5051,11 +5051,11 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>11 Sep live check</t>
+          <t>11 Sep live check; includes the freelancer query, won on AI Mode</t>
         </is>
       </c>
     </row>

--- a/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
+++ b/docs/seo/designbees-aeo-seo-tracker-2026-09-10.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Task Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tasks" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sources" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evergreen Pages" sheetId="4" state="visible" r:id="rId4"/>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTA('Task Tracker'!$A$5:$A$1000)</f>
+        <f>COUNTA(Tasks!$A$5:$A$1000)</f>
         <v/>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIF('Task Tracker'!$B$5:$B$1000,D5)</f>
+        <f>COUNTIF(Tasks!$B$5:$B$1000,D5)</f>
         <v/>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>COUNTIF('Task Tracker'!$C$5:$C$1000,"Done")</f>
+        <f>COUNTIF(Tasks!$C$5:$C$1000,"Done")</f>
         <v/>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIF('Task Tracker'!$B$5:$B$1000,D6)</f>
+        <f>COUNTIF(Tasks!$B$5:$B$1000,D6)</f>
         <v/>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>COUNTIF('Task Tracker'!$C$5:$C$1000,"In progress")</f>
+        <f>COUNTIF(Tasks!$C$5:$C$1000,"In progress")</f>
         <v/>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIF('Task Tracker'!$B$5:$B$1000,D7)</f>
+        <f>COUNTIF(Tasks!$B$5:$B$1000,D7)</f>
         <v/>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF('Task Tracker'!$C$5:$C$1000,"Blocked")</f>
+        <f>COUNTIF(Tasks!$C$5:$C$1000,"Blocked")</f>
         <v/>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF('Task Tracker'!$C$5:$C$1000,"Needs verification")</f>
+        <f>COUNTIF(Tasks!$C$5:$C$1000,"Needs verification")</f>
         <v/>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Start with the P0 tasks on the Task Tracker tab. Set Status as you work in Wix; use "Needs verification" until the Verification column check has been done on the live site or in Search Console. Evergreen Pages lists the pages that answer the six target questions and which are still to build. Sources holds every evidence and implementation link. Tracking is the monthly log: add a row per metric each month with the same inputs, and the Latest block updates itself. Full report: https://claude.ai/code/artifact/e3ddf06b-bfc3-4925-92d9-458fc2c3dfb2</t>
+          <t>Start with the P0 tasks on the Tasks tab. Set Status as you work in Wix; use "Needs verification" until the Verification column check has been done on the live site or in Search Console. Evergreen Pages lists the pages that answer the six target questions and which are still to build. Sources holds every evidence and implementation link. Tracking is the monthly log: add a row per metric each month with the same inputs, and the Latest block updates itself. Full report: https://claude.ai/code/artifact/e3ddf06b-bfc3-4925-92d9-458fc2c3dfb2</t>
         </is>
       </c>
     </row>
